--- a/public/excel_template/site.xlsx
+++ b/public/excel_template/site.xlsx
@@ -7,16 +7,14 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eZmG/9xbigqurZMK+0jxVjFGOPjYHzEtEfIAbHEhhsY="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>metro_status</t>
+  </si>
   <si>
     <t>Location</t>
   </si>
@@ -64,70 +62,16 @@
   </si>
   <si>
     <t>Designation</t>
-  </si>
-  <si>
-    <t>Deoria</t>
-  </si>
-  <si>
-    <t>Sashank Tripathi</t>
-  </si>
-  <si>
-    <t>asdf@gmail.com</t>
-  </si>
-  <si>
-    <t>office</t>
-  </si>
-  <si>
-    <t>1/123 sector N</t>
-  </si>
-  <si>
-    <t>Uttar Pradesh</t>
-  </si>
-  <si>
-    <t>16-02-2022</t>
-  </si>
-  <si>
-    <t>16-02-2024</t>
-  </si>
-  <si>
-    <t>Aakansh Dubey</t>
-  </si>
-  <si>
-    <t>AFM</t>
-  </si>
-  <si>
-    <t>Lucknow</t>
-  </si>
-  <si>
-    <t>Rahul Singh</t>
-  </si>
-  <si>
-    <t>asas@gmail.com</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>1/89,sector m</t>
-  </si>
-  <si>
-    <t>16-02-2020</t>
-  </si>
-  <si>
-    <t>16-02-2026</t>
-  </si>
-  <si>
-    <t>Abhishek Kumar</t>
-  </si>
-  <si>
-    <t>AGM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m-d-yyyy"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -151,11 +95,6 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -171,9 +110,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -181,7 +123,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -396,201 +340,233 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="13.75"/>
-    <col customWidth="1" min="4" max="4" width="14.13"/>
-    <col customWidth="1" min="5" max="5" width="19.0"/>
-    <col customWidth="1" min="6" max="6" width="12.63"/>
-    <col customWidth="1" min="11" max="11" width="20.88"/>
-    <col customWidth="1" min="12" max="12" width="21.0"/>
-    <col customWidth="1" min="15" max="15" width="20.63"/>
+    <col customWidth="1" min="1" max="3" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="13.75"/>
+    <col customWidth="1" min="5" max="5" width="14.13"/>
+    <col customWidth="1" min="6" max="6" width="19.0"/>
+    <col customWidth="1" min="7" max="7" width="12.63"/>
+    <col customWidth="1" min="12" max="12" width="20.88"/>
+    <col customWidth="1" min="13" max="13" width="21.0"/>
+    <col customWidth="1" min="16" max="16" width="20.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1001.0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4">
-        <v>9.87654321E9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="4">
-        <v>274404.0</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="4">
-        <v>123456.0</v>
-      </c>
-      <c r="N2" s="4">
-        <v>123456.0</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1002.0</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4">
-        <v>9.876543211E9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="4">
-        <v>226021.0</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="4">
-        <v>78910.0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>78910.0</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>

--- a/public/excel_template/site.xlsx
+++ b/public/excel_template/site.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>metro_status</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Location</t>
   </si>
@@ -110,12 +107,9 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -340,233 +334,228 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="13.75"/>
-    <col customWidth="1" min="5" max="5" width="14.13"/>
-    <col customWidth="1" min="6" max="6" width="19.0"/>
-    <col customWidth="1" min="7" max="7" width="12.63"/>
-    <col customWidth="1" min="12" max="12" width="20.88"/>
-    <col customWidth="1" min="13" max="13" width="21.0"/>
-    <col customWidth="1" min="16" max="16" width="20.63"/>
+    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="3" max="3" width="13.75"/>
+    <col customWidth="1" min="4" max="4" width="14.13"/>
+    <col customWidth="1" min="5" max="5" width="19.0"/>
+    <col customWidth="1" min="6" max="6" width="12.63"/>
+    <col customWidth="1" min="11" max="11" width="20.88"/>
+    <col customWidth="1" min="12" max="12" width="21.0"/>
+    <col customWidth="1" min="15" max="15" width="20.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="K4" s="4"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="K8" s="4"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="5"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
